--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
@@ -3,19 +3,35 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14160" windowHeight="2175"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>交收流水序号</t>
+  </si>
+  <si>
+    <t>交收日期</t>
+  </si>
+  <si>
+    <t>交收时间</t>
+  </si>
+  <si>
+    <t>交易时间</t>
+  </si>
   <si>
     <t>交收状态</t>
   </si>
@@ -26,53 +42,73 @@
     <t>原业务编号</t>
   </si>
   <si>
-    <t>交易日期</t>
-  </si>
-  <si>
-    <t>交收日期</t>
+    <t>资金账户</t>
+  </si>
+  <si>
+    <t>证券账户</t>
+  </si>
+  <si>
+    <t>交易市场</t>
+  </si>
+  <si>
+    <t>交易平台</t>
+  </si>
+  <si>
+    <t>资产代码</t>
+  </si>
+  <si>
+    <t>资产名称</t>
+  </si>
+  <si>
+    <t>交收数量</t>
+  </si>
+  <si>
+    <t>交收金额</t>
+  </si>
+  <si>
+    <t>回购金额</t>
+  </si>
+  <si>
+    <t>到期结算金额</t>
+  </si>
+  <si>
+    <t>质押券代码</t>
+  </si>
+  <si>
+    <t>质押券名称</t>
+  </si>
+  <si>
+    <t>质押数量</t>
+  </si>
+  <si>
+    <t>原质押券代码</t>
+  </si>
+  <si>
+    <t>业务类别</t>
+  </si>
+  <si>
+    <t>交易对手</t>
+  </si>
+  <si>
+    <t>操作类型</t>
+  </si>
+  <si>
+    <t>操作员</t>
   </si>
   <si>
     <t>组合代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>组合名称</t>
-  </si>
-  <si>
-    <t>资金账户</t>
-  </si>
-  <si>
-    <t>证券账户</t>
-  </si>
-  <si>
-    <t>交易市场</t>
-  </si>
-  <si>
-    <t>交易平台</t>
-  </si>
-  <si>
-    <t>资产代码</t>
-  </si>
-  <si>
-    <t>资产名称</t>
-  </si>
-  <si>
-    <t>交割数量</t>
-  </si>
-  <si>
-    <t>交割金额</t>
-  </si>
-  <si>
-    <t>业务类别</t>
-  </si>
-  <si>
-    <t>交易对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,36 +117,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -118,35 +139,86 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -166,7 +238,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -201,7 +273,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +308,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -445,69 +517,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="17" width="15.625" customWidth="1"/>
+    <col min="1" max="4" width="11.75" customWidth="1"/>
+    <col min="7" max="8" width="11.75" customWidth="1"/>
+    <col min="19" max="19" width="13.75" customWidth="1"/>
+    <col min="20" max="20" width="11.875" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="23" max="23" width="11.75" customWidth="1"/>
+    <col min="25" max="25" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
+      <c r="T1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
@@ -1,106 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11865" windowHeight="6645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>交收流水序号</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>交收状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原业务编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>证券账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易市场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交收日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交收时间</t>
-  </si>
-  <si>
-    <t>交易时间</t>
-  </si>
-  <si>
-    <t>交收状态</t>
-  </si>
-  <si>
-    <t>指令序号</t>
-  </si>
-  <si>
-    <t>原业务编号</t>
-  </si>
-  <si>
-    <t>资金账户</t>
-  </si>
-  <si>
-    <t>证券账户</t>
-  </si>
-  <si>
-    <t>交易市场</t>
-  </si>
-  <si>
-    <t>交易平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资产代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交收数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交收金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>回购金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>到期结算金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>质押券代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>质押券名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>质押数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>原质押券代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>业务类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交易对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>操作类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>操作员</t>
-  </si>
-  <si>
-    <t>组合代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -113,12 +129,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -143,82 +160,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -238,7 +188,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -273,7 +223,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,7 +258,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -517,54 +467,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="11.75" customWidth="1"/>
-    <col min="7" max="8" width="11.75" customWidth="1"/>
-    <col min="19" max="19" width="13.75" customWidth="1"/>
-    <col min="20" max="20" width="11.875" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="23" max="23" width="11.75" customWidth="1"/>
-    <col min="25" max="25" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
+    <col min="18" max="18" width="13.75" customWidth="1"/>
+    <col min="19" max="19" width="11.875" customWidth="1"/>
+    <col min="20" max="20" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="11.75" customWidth="1"/>
+    <col min="24" max="24" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
       </c>
       <c r="M1" t="s">
         <v>10</v>
@@ -607,9 +558,6 @@
       </c>
       <c r="Z1" t="s">
         <v>23</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
